--- a/data/trans_orig/IP07C18-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP07C18-Habitat-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de llevarse bien con los profesores en 2007 (tasa de respuesta: 89,49%)</t>
+          <t>Menores según la frecuencia de llevarse bien con el profesorado en 2007 (tasa de respuesta: 89,49%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>21789</t>
+          <t>21817</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>34595</t>
+          <t>34051</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>37,89%</t>
+          <t>37,94%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>60,16%</t>
+          <t>59,22%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>19022</t>
+          <t>18996</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>32452</t>
+          <t>31896</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>27,99%</t>
+          <t>27,95%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>47,75%</t>
+          <t>46,93%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>44129</t>
+          <t>43964</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>62655</t>
+          <t>62330</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>35,17%</t>
+          <t>35,04%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>49,94%</t>
+          <t>49,68%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>14988</t>
+          <t>14763</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>26872</t>
+          <t>26915</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>26,06%</t>
+          <t>25,67%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>46,73%</t>
+          <t>46,81%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>17337</t>
+          <t>17963</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>30198</t>
+          <t>30328</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>25,51%</t>
+          <t>26,43%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>44,43%</t>
+          <t>44,62%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>35169</t>
+          <t>35635</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>52861</t>
+          <t>52781</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>28,03%</t>
+          <t>28,4%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>42,13%</t>
+          <t>42,07%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>5169</t>
+          <t>5190</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>14519</t>
+          <t>14433</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>8,99%</t>
+          <t>9,03%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>25,25%</t>
+          <t>25,1%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>10424</t>
+          <t>9873</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>21464</t>
+          <t>20844</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>15,34%</t>
+          <t>14,53%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>31,58%</t>
+          <t>30,67%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>18406</t>
+          <t>17751</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>31890</t>
+          <t>31614</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>14,67%</t>
+          <t>14,15%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>25,42%</t>
+          <t>25,2%</t>
         </is>
       </c>
     </row>
@@ -1106,12 +1106,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1262</t>
+          <t>1191</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7860</t>
+          <t>7274</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1121,12 +1121,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>11,56%</t>
+          <t>10,7%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1190</t>
+          <t>1240</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>7601</t>
+          <t>7504</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>5,98%</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>3267</t>
+          <t>3299</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,85%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,7 +1259,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3282</t>
+          <t>3297</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,63%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>28091</t>
+          <t>28234</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>42537</t>
+          <t>42730</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>28,51%</t>
+          <t>28,65%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>43,17%</t>
+          <t>43,36%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>24210</t>
+          <t>24887</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>38538</t>
+          <t>39069</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>26,29%</t>
+          <t>27,02%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>41,84%</t>
+          <t>42,42%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>56787</t>
+          <t>56934</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>78029</t>
+          <t>76893</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>29,79%</t>
+          <t>29,86%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>40,93%</t>
+          <t>40,33%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>36986</t>
+          <t>37434</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>51882</t>
+          <t>51941</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>37,53%</t>
+          <t>37,99%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>52,65%</t>
+          <t>52,71%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>25562</t>
+          <t>25715</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>40808</t>
+          <t>40700</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>27,75%</t>
+          <t>27,92%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>44,31%</t>
+          <t>44,19%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>67376</t>
+          <t>66744</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>88781</t>
+          <t>88698</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>35,34%</t>
+          <t>35,01%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>46,57%</t>
+          <t>46,53%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>10201</t>
+          <t>9812</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>21392</t>
+          <t>20654</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>10,35%</t>
+          <t>9,96%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>21,71%</t>
+          <t>20,96%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>16804</t>
+          <t>16735</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>30007</t>
+          <t>29182</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>18,24%</t>
+          <t>18,17%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>32,58%</t>
+          <t>31,68%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>29026</t>
+          <t>29914</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>46077</t>
+          <t>46632</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>15,23%</t>
+          <t>15,69%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>24,17%</t>
+          <t>24,46%</t>
         </is>
       </c>
     </row>
@@ -1758,7 +1758,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3522</t>
+          <t>3971</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1773,7 +1773,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1788,12 +1788,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>593</t>
+          <t>592</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5190</t>
+          <t>5218</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1808,7 +1808,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>5,66%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1180</t>
+          <t>1183</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>6988</t>
+          <t>6441</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,38%</t>
         </is>
       </c>
     </row>
@@ -1866,12 +1866,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>689</t>
+          <t>670</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>6588</t>
+          <t>6685</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1881,12 +1881,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>6,78%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1901,12 +1901,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1259</t>
+          <t>1256</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>7155</t>
+          <t>7167</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1916,47 +1916,47 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
+          <t>1,36%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>7,78%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>5920</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>2614</t>
+        </is>
+      </c>
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>10239</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>3,11%</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
           <t>1,37%</t>
         </is>
       </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>7,77%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>5920</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>3163</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>11036</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>3,11%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>1,66%</t>
-        </is>
-      </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>5,37%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>23877</t>
+          <t>23837</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>34836</t>
+          <t>35062</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>43,4%</t>
+          <t>43,32%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>63,31%</t>
+          <t>63,73%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>20474</t>
+          <t>21391</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>33393</t>
+          <t>33036</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>34,16%</t>
+          <t>35,69%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>55,71%</t>
+          <t>55,12%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>47705</t>
+          <t>48554</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>64238</t>
+          <t>65899</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>41,5%</t>
+          <t>42,24%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>55,88%</t>
+          <t>57,32%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>9432</t>
+          <t>9386</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>19224</t>
+          <t>19378</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>17,14%</t>
+          <t>17,06%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>34,94%</t>
+          <t>35,22%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>16599</t>
+          <t>17018</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>28002</t>
+          <t>28650</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>27,69%</t>
+          <t>28,39%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>46,72%</t>
+          <t>47,8%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>28669</t>
+          <t>27915</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>44718</t>
+          <t>44705</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>24,94%</t>
+          <t>24,28%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>38,9%</t>
+          <t>38,89%</t>
         </is>
       </c>
     </row>
@@ -2322,12 +2322,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>5565</t>
+          <t>5863</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>13774</t>
+          <t>14199</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>10,11%</t>
+          <t>10,66%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>25,03%</t>
+          <t>25,81%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>4558</t>
+          <t>3965</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>12898</t>
+          <t>12469</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>7,61%</t>
+          <t>6,62%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>21,52%</t>
+          <t>20,8%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>12532</t>
+          <t>12226</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>24083</t>
+          <t>24236</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>10,9%</t>
+          <t>10,64%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>20,95%</t>
+          <t>21,08%</t>
         </is>
       </c>
     </row>
@@ -2440,7 +2440,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4232</t>
+          <t>4015</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2455,7 +2455,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>7,69%</t>
+          <t>7,3%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2475,7 +2475,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>3581</t>
+          <t>3996</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2490,7 +2490,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>6,67%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,7 +2510,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>4509</t>
+          <t>4194</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2525,7 +2525,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>3,65%</t>
         </is>
       </c>
     </row>
@@ -2553,7 +2553,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>4378</t>
+          <t>3799</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2568,7 +2568,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>7,96%</t>
+          <t>6,9%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2583,12 +2583,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>638</t>
+          <t>652</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>5432</t>
+          <t>5507</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2598,12 +2598,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>9,06%</t>
+          <t>9,19%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2618,12 +2618,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1275</t>
+          <t>1269</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>7253</t>
+          <t>7250</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2633,7 +2633,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>20056</t>
+          <t>20536</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>34532</t>
+          <t>34840</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>25,61%</t>
+          <t>26,22%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>44,1%</t>
+          <t>44,49%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>19567</t>
+          <t>18948</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>33433</t>
+          <t>33650</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>22,2%</t>
+          <t>21,5%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>37,94%</t>
+          <t>38,18%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>44365</t>
+          <t>43650</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>62753</t>
+          <t>63895</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>26,66%</t>
+          <t>26,23%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>37,7%</t>
+          <t>38,39%</t>
         </is>
       </c>
     </row>
@@ -2891,12 +2891,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>28522</t>
+          <t>27958</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>44410</t>
+          <t>42795</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2906,12 +2906,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>36,42%</t>
+          <t>35,7%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>56,71%</t>
+          <t>54,65%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2926,12 +2926,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>34610</t>
+          <t>34500</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>49521</t>
+          <t>49519</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2941,7 +2941,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>39,27%</t>
+          <t>39,15%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>66360</t>
+          <t>66900</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>87930</t>
+          <t>87524</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2976,12 +2976,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>39,87%</t>
+          <t>40,2%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>52,83%</t>
+          <t>52,59%</t>
         </is>
       </c>
     </row>
@@ -3004,12 +3004,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>5341</t>
+          <t>4867</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>15338</t>
+          <t>14895</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3019,12 +3019,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>6,21%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>19,59%</t>
+          <t>19,02%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3039,12 +3039,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>8608</t>
+          <t>9380</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>19647</t>
+          <t>20140</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3054,12 +3054,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>9,77%</t>
+          <t>10,64%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>22,29%</t>
+          <t>22,85%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>16454</t>
+          <t>16864</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>30884</t>
+          <t>31737</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3089,12 +3089,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>9,89%</t>
+          <t>10,13%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>18,56%</t>
+          <t>19,07%</t>
         </is>
       </c>
     </row>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>4779</t>
+          <t>5090</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3137,7 +3137,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3152,12 +3152,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>705</t>
+          <t>698</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>6617</t>
+          <t>6423</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3167,12 +3167,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>7,29%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3187,12 +3187,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1515</t>
+          <t>1991</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>9552</t>
+          <t>8650</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3202,12 +3202,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>5,2%</t>
         </is>
       </c>
     </row>
@@ -3230,12 +3230,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2150</t>
+          <t>2141</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>9491</t>
+          <t>9448</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3245,12 +3245,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>12,12%</t>
+          <t>12,06%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3265,12 +3265,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1155</t>
+          <t>1214</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>6839</t>
+          <t>6384</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>7,76%</t>
+          <t>7,24%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3300,12 +3300,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>4598</t>
+          <t>4697</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>13856</t>
+          <t>13850</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>8,33%</t>
+          <t>8,32%</t>
         </is>
       </c>
     </row>
@@ -3460,12 +3460,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>107079</t>
+          <t>107153</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>133195</t>
+          <t>133447</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3475,12 +3475,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>37,0%</t>
+          <t>37,03%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>46,03%</t>
+          <t>46,12%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3495,12 +3495,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>95034</t>
+          <t>95579</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>122540</t>
+          <t>123528</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3510,12 +3510,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>30,84%</t>
+          <t>31,02%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>39,77%</t>
+          <t>40,09%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3530,12 +3530,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>211492</t>
+          <t>211827</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>249283</t>
+          <t>248763</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3545,12 +3545,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>35,4%</t>
+          <t>35,45%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>41,72%</t>
+          <t>41,63%</t>
         </is>
       </c>
     </row>
@@ -3573,12 +3573,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>101109</t>
+          <t>102148</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>127511</t>
+          <t>127650</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3588,12 +3588,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>34,94%</t>
+          <t>35,3%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>44,06%</t>
+          <t>44,11%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>108062</t>
+          <t>107611</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>135311</t>
+          <t>134636</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3623,12 +3623,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>35,07%</t>
+          <t>34,92%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>43,91%</t>
+          <t>43,69%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3643,12 +3643,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>216361</t>
+          <t>215970</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>255334</t>
+          <t>253998</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3658,12 +3658,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>36,21%</t>
+          <t>36,14%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>42,73%</t>
+          <t>42,51%</t>
         </is>
       </c>
     </row>
@@ -3686,12 +3686,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>33489</t>
+          <t>33324</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>54559</t>
+          <t>53354</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3701,12 +3701,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>11,57%</t>
+          <t>11,52%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>18,85%</t>
+          <t>18,44%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3721,12 +3721,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>49412</t>
+          <t>48978</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>72002</t>
+          <t>71112</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3736,12 +3736,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>16,04%</t>
+          <t>15,89%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>23,37%</t>
+          <t>23,08%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3756,12 +3756,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>88242</t>
+          <t>88083</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>117276</t>
+          <t>117433</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3771,12 +3771,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>14,77%</t>
+          <t>14,74%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>19,63%</t>
+          <t>19,65%</t>
         </is>
       </c>
     </row>
@@ -3799,12 +3799,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>1210</t>
+          <t>1134</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>7759</t>
+          <t>7246</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3814,12 +3814,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3834,12 +3834,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>5404</t>
+          <t>5182</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>15403</t>
+          <t>15657</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3849,12 +3849,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>5,08%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3869,12 +3869,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>7241</t>
+          <t>7642</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>18789</t>
+          <t>19419</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3884,12 +3884,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,25%</t>
         </is>
       </c>
     </row>
@@ -3912,12 +3912,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>4923</t>
+          <t>4899</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>15623</t>
+          <t>15142</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3927,12 +3927,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3947,12 +3947,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>5182</t>
+          <t>5082</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>15173</t>
+          <t>14757</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3962,12 +3962,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>4,79%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3982,12 +3982,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>12223</t>
+          <t>11896</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>25761</t>
+          <t>24929</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,17%</t>
         </is>
       </c>
     </row>
@@ -4179,7 +4179,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de llevarse bien con los profesores en 2012 (tasa de respuesta: 95,31%)</t>
+          <t>Menores según la frecuencia de llevarse bien con el profesorado en 2012 (tasa de respuesta: 95,31%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4374,12 +4374,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>36092</t>
+          <t>36123</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>48721</t>
+          <t>48879</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4389,12 +4389,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>56,89%</t>
+          <t>56,94%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>76,79%</t>
+          <t>77,04%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4409,12 +4409,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>29581</t>
+          <t>29954</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>44257</t>
+          <t>44277</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4424,12 +4424,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>41,1%</t>
+          <t>41,62%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>61,49%</t>
+          <t>61,52%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4444,12 +4444,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>69361</t>
+          <t>69930</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>88998</t>
+          <t>88599</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4459,12 +4459,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>51,22%</t>
+          <t>51,64%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>65,72%</t>
+          <t>65,42%</t>
         </is>
       </c>
     </row>
@@ -4487,12 +4487,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>8406</t>
+          <t>8935</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>19851</t>
+          <t>19779</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4502,12 +4502,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>13,25%</t>
+          <t>14,08%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>31,29%</t>
+          <t>31,18%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4522,12 +4522,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>22142</t>
+          <t>22020</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>36441</t>
+          <t>36007</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4537,12 +4537,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>30,76%</t>
+          <t>30,59%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>50,63%</t>
+          <t>50,03%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4557,12 +4557,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>34309</t>
+          <t>34209</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>52940</t>
+          <t>51660</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4572,12 +4572,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>25,33%</t>
+          <t>25,26%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>39,09%</t>
+          <t>38,15%</t>
         </is>
       </c>
     </row>
@@ -4600,12 +4600,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1580</t>
+          <t>1979</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>9577</t>
+          <t>8689</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4615,12 +4615,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>15,1%</t>
+          <t>13,69%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4635,12 +4635,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>2560</t>
+          <t>2680</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>9858</t>
+          <t>10561</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4650,12 +4650,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>13,7%</t>
+          <t>14,67%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4670,12 +4670,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>5478</t>
+          <t>5233</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>15074</t>
+          <t>15700</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>11,13%</t>
+          <t>11,59%</t>
         </is>
       </c>
     </row>
@@ -4718,7 +4718,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5761</t>
+          <t>5245</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4733,7 +4733,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,08%</t>
+          <t>8,27%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4753,7 +4753,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3157</t>
+          <t>3201</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4783,12 +4783,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>630</t>
+          <t>633</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>5901</t>
+          <t>6834</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>5,05%</t>
         </is>
       </c>
     </row>
@@ -4831,7 +4831,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>3571</t>
+          <t>3585</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4846,7 +4846,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4901,7 +4901,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3774</t>
+          <t>3598</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4916,7 +4916,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,66%</t>
         </is>
       </c>
     </row>
@@ -5056,12 +5056,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>46892</t>
+          <t>46346</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>62240</t>
+          <t>61890</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5071,12 +5071,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>48,25%</t>
+          <t>47,69%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>64,05%</t>
+          <t>63,68%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5091,12 +5091,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>39949</t>
+          <t>39186</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>54994</t>
+          <t>54945</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5106,12 +5106,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>42,27%</t>
+          <t>41,46%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>58,18%</t>
+          <t>58,13%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5126,12 +5126,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>91131</t>
+          <t>90046</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>112183</t>
+          <t>111893</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5141,12 +5141,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>47,54%</t>
+          <t>46,97%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>58,52%</t>
+          <t>58,37%</t>
         </is>
       </c>
     </row>
@@ -5169,12 +5169,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>22385</t>
+          <t>22414</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>36648</t>
+          <t>37225</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5184,12 +5184,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>23,03%</t>
+          <t>23,06%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>37,71%</t>
+          <t>38,3%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5204,12 +5204,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>25571</t>
+          <t>25406</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>40278</t>
+          <t>40644</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5219,12 +5219,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>27,05%</t>
+          <t>26,88%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>42,61%</t>
+          <t>43,0%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5239,12 +5239,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>51583</t>
+          <t>52245</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>72763</t>
+          <t>72567</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5254,12 +5254,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>26,91%</t>
+          <t>27,25%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>37,96%</t>
+          <t>37,85%</t>
         </is>
       </c>
     </row>
@@ -5282,12 +5282,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>6461</t>
+          <t>6332</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>15067</t>
+          <t>16353</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5297,82 +5297,82 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
+          <t>6,52%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>16,83%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>8624</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>4908</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>14683</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>9,12%</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>5,19%</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>15,53%</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="R12" s="2" t="inlineStr">
+        <is>
+          <t>18906</t>
+        </is>
+      </c>
+      <c r="S12" s="2" t="inlineStr">
+        <is>
+          <t>12755</t>
+        </is>
+      </c>
+      <c r="T12" s="2" t="inlineStr">
+        <is>
+          <t>26244</t>
+        </is>
+      </c>
+      <c r="U12" s="2" t="inlineStr">
+        <is>
+          <t>9,86%</t>
+        </is>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
           <t>6,65%</t>
         </is>
       </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>15,5%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>8624</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>4632</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>14210</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>9,12%</t>
-        </is>
-      </c>
-      <c r="O12" s="2" t="inlineStr">
-        <is>
-          <t>4,9%</t>
-        </is>
-      </c>
-      <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>15,03%</t>
-        </is>
-      </c>
-      <c r="Q12" s="2" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="R12" s="2" t="inlineStr">
-        <is>
-          <t>18906</t>
-        </is>
-      </c>
-      <c r="S12" s="2" t="inlineStr">
-        <is>
-          <t>12800</t>
-        </is>
-      </c>
-      <c r="T12" s="2" t="inlineStr">
-        <is>
-          <t>27018</t>
-        </is>
-      </c>
-      <c r="U12" s="2" t="inlineStr">
-        <is>
-          <t>9,86%</t>
-        </is>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>6,68%</t>
-        </is>
-      </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>14,09%</t>
+          <t>13,69%</t>
         </is>
       </c>
     </row>
@@ -5400,7 +5400,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4022</t>
+          <t>3375</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5415,7 +5415,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5430,12 +5430,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>660</t>
+          <t>665</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>6409</t>
+          <t>5945</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5450,7 +5450,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>6,29%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5465,12 +5465,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1247</t>
+          <t>1244</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>7266</t>
+          <t>7422</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5485,7 +5485,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,87%</t>
         </is>
       </c>
     </row>
@@ -5508,12 +5508,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>659</t>
+          <t>671</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>6646</t>
+          <t>6647</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5523,7 +5523,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -5543,12 +5543,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1308</t>
+          <t>1346</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>7813</t>
+          <t>7662</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5558,12 +5558,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>8,27%</t>
+          <t>8,11%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5578,12 +5578,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>3211</t>
+          <t>2686</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>11359</t>
+          <t>10898</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5593,12 +5593,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>5,69%</t>
         </is>
       </c>
     </row>
@@ -5738,12 +5738,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>29989</t>
+          <t>30505</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>42791</t>
+          <t>43134</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5753,12 +5753,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>46,02%</t>
+          <t>46,81%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>65,66%</t>
+          <t>66,19%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5773,12 +5773,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>37514</t>
+          <t>36574</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>49370</t>
+          <t>49817</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5788,12 +5788,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>54,82%</t>
+          <t>53,45%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>72,15%</t>
+          <t>72,8%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5808,12 +5808,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>71022</t>
+          <t>71419</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>90312</t>
+          <t>89049</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5823,12 +5823,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>53,16%</t>
+          <t>53,46%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>67,6%</t>
+          <t>66,66%</t>
         </is>
       </c>
     </row>
@@ -5851,12 +5851,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>12699</t>
+          <t>12433</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>24492</t>
+          <t>23806</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5866,12 +5866,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>19,49%</t>
+          <t>19,08%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>37,58%</t>
+          <t>36,53%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5886,12 +5886,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>13245</t>
+          <t>12535</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>24869</t>
+          <t>24605</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5901,12 +5901,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>19,36%</t>
+          <t>18,32%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>36,34%</t>
+          <t>35,96%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5921,12 +5921,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>28432</t>
+          <t>29286</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>45951</t>
+          <t>45362</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5936,12 +5936,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>21,28%</t>
+          <t>21,92%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>34,4%</t>
+          <t>33,95%</t>
         </is>
       </c>
     </row>
@@ -5964,12 +5964,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3254</t>
+          <t>3200</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>11205</t>
+          <t>10750</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5979,12 +5979,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>17,19%</t>
+          <t>16,5%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5999,12 +5999,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>641</t>
+          <t>609</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>6424</t>
+          <t>6205</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>9,39%</t>
+          <t>9,07%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>4863</t>
+          <t>4739</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>14256</t>
+          <t>14370</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>10,67%</t>
+          <t>10,76%</t>
         </is>
       </c>
     </row>
@@ -6082,7 +6082,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4536</t>
+          <t>4354</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -6097,7 +6097,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>6,68%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -6112,12 +6112,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>553</t>
+          <t>546</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>4063</t>
+          <t>5128</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>7,49%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1154</t>
+          <t>1136</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>6799</t>
+          <t>6628</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>4,96%</t>
         </is>
       </c>
     </row>
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>664</t>
+          <t>682</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>6308</t>
+          <t>6627</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6205,12 +6205,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>9,68%</t>
+          <t>10,17%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6225,12 +6225,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>601</t>
+          <t>595</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>5444</t>
+          <t>4306</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6240,12 +6240,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>7,96%</t>
+          <t>6,29%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6260,12 +6260,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1898</t>
+          <t>1891</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>8897</t>
+          <t>8984</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6280,7 +6280,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>6,73%</t>
         </is>
       </c>
     </row>
@@ -6420,12 +6420,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>32426</t>
+          <t>33153</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>48611</t>
+          <t>48613</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6435,7 +6435,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>37,83%</t>
+          <t>38,67%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -6455,12 +6455,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>32832</t>
+          <t>32848</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>48331</t>
+          <t>48446</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6470,12 +6470,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>36,93%</t>
+          <t>36,95%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>54,36%</t>
+          <t>54,49%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6490,12 +6490,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>69861</t>
+          <t>69765</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>92343</t>
+          <t>92138</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6505,12 +6505,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>40,01%</t>
+          <t>39,95%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>52,88%</t>
+          <t>52,76%</t>
         </is>
       </c>
     </row>
@@ -6533,12 +6533,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>24852</t>
+          <t>24526</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>39954</t>
+          <t>39942</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6548,12 +6548,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>28,99%</t>
+          <t>28,61%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>46,61%</t>
+          <t>46,59%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6568,12 +6568,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>24843</t>
+          <t>25269</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>40602</t>
+          <t>40666</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>27,94%</t>
+          <t>28,42%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>45,67%</t>
+          <t>45,74%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6603,12 +6603,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>55230</t>
+          <t>54118</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>77502</t>
+          <t>76621</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6618,12 +6618,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>31,63%</t>
+          <t>30,99%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>44,38%</t>
+          <t>43,88%</t>
         </is>
       </c>
     </row>
@@ -6646,12 +6646,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>5505</t>
+          <t>5532</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>15906</t>
+          <t>16583</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6661,12 +6661,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>6,45%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>18,55%</t>
+          <t>19,34%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6681,12 +6681,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>7221</t>
+          <t>7381</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>18062</t>
+          <t>18154</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6696,12 +6696,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>20,32%</t>
+          <t>20,42%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6716,12 +6716,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>15562</t>
+          <t>15000</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>30723</t>
+          <t>29858</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6731,12 +6731,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>8,91%</t>
+          <t>8,59%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>17,59%</t>
+          <t>17,1%</t>
         </is>
       </c>
     </row>
@@ -6764,7 +6764,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>6398</t>
+          <t>7536</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6779,7 +6779,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>8,79%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6799,7 +6799,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>4785</t>
+          <t>5197</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6814,7 +6814,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6829,12 +6829,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>777</t>
+          <t>781</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>8315</t>
+          <t>7778</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6844,12 +6844,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,45%</t>
         </is>
       </c>
     </row>
@@ -6877,7 +6877,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3433</t>
+          <t>3792</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6892,7 +6892,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6907,12 +6907,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>614</t>
+          <t>618</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>5828</t>
+          <t>5804</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6922,12 +6922,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>6,53%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6942,12 +6942,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>701</t>
+          <t>746</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6425</t>
+          <t>6680</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6957,12 +6957,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,83%</t>
         </is>
       </c>
     </row>
@@ -7102,12 +7102,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>159797</t>
+          <t>160995</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>188713</t>
+          <t>189272</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>51,3%</t>
+          <t>51,68%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>60,58%</t>
+          <t>60,76%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7137,12 +7137,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>153968</t>
+          <t>153186</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>185066</t>
+          <t>183035</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7152,12 +7152,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>47,55%</t>
+          <t>47,3%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>57,15%</t>
+          <t>56,52%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7172,12 +7172,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>322703</t>
+          <t>321517</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>364618</t>
+          <t>363346</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7187,12 +7187,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>50,79%</t>
+          <t>50,61%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>57,39%</t>
+          <t>57,19%</t>
         </is>
       </c>
     </row>
@@ -7215,12 +7215,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>80858</t>
+          <t>80531</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>107695</t>
+          <t>106827</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>25,96%</t>
+          <t>25,85%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>34,57%</t>
+          <t>34,29%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7250,12 +7250,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>97654</t>
+          <t>99083</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>127103</t>
+          <t>128469</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7265,12 +7265,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>30,16%</t>
+          <t>30,6%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>39,25%</t>
+          <t>39,67%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7285,12 +7285,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>186192</t>
+          <t>188936</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>227435</t>
+          <t>227984</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7300,12 +7300,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>29,31%</t>
+          <t>29,74%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>35,8%</t>
+          <t>35,88%</t>
         </is>
       </c>
     </row>
@@ -7328,12 +7328,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>22906</t>
+          <t>22791</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>40423</t>
+          <t>40350</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7343,12 +7343,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>7,32%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>12,98%</t>
+          <t>12,95%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7363,12 +7363,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>21633</t>
+          <t>20850</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>38065</t>
+          <t>38003</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7378,12 +7378,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>6,44%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>11,75%</t>
+          <t>11,74%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7398,12 +7398,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>48279</t>
+          <t>48450</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>71579</t>
+          <t>73489</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7413,12 +7413,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>7,63%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>11,27%</t>
+          <t>11,57%</t>
         </is>
       </c>
     </row>
@@ -7441,12 +7441,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>2284</t>
+          <t>2508</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>11063</t>
+          <t>11727</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -7456,12 +7456,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -7476,12 +7476,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>2993</t>
+          <t>3308</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>11306</t>
+          <t>11986</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -7491,12 +7491,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -7511,12 +7511,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>7037</t>
+          <t>6948</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>18493</t>
+          <t>18789</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -7526,12 +7526,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,96%</t>
         </is>
       </c>
     </row>
@@ -7554,12 +7554,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>3289</t>
+          <t>3390</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>11438</t>
+          <t>11733</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -7569,12 +7569,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -7589,12 +7589,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>3943</t>
+          <t>3955</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>12627</t>
+          <t>13342</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -7609,7 +7609,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -7624,12 +7624,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>8775</t>
+          <t>8783</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>20914</t>
+          <t>21362</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -7644,7 +7644,7 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,36%</t>
         </is>
       </c>
     </row>
@@ -7821,7 +7821,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de llevarse bien con los profesores en 2016 (tasa de respuesta: 95,18%)</t>
+          <t>Menores según la frecuencia de llevarse bien con el profesorado en 2016 (tasa de respuesta: 95,18%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8016,12 +8016,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>24410</t>
+          <t>24418</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>37768</t>
+          <t>38581</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8031,12 +8031,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>35,37%</t>
+          <t>35,39%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>54,73%</t>
+          <t>55,91%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8051,12 +8051,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>25998</t>
+          <t>24960</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>40635</t>
+          <t>39743</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8066,12 +8066,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>36,6%</t>
+          <t>35,13%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>57,2%</t>
+          <t>55,94%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8086,12 +8086,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>54325</t>
+          <t>53947</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>74436</t>
+          <t>74008</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8101,12 +8101,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>38,79%</t>
+          <t>38,52%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>53,15%</t>
+          <t>52,85%</t>
         </is>
       </c>
     </row>
@@ -8129,12 +8129,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>23789</t>
+          <t>23568</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>37935</t>
+          <t>37586</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8144,12 +8144,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>34,48%</t>
+          <t>34,16%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>54,98%</t>
+          <t>54,47%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8164,12 +8164,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>21353</t>
+          <t>22088</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>36002</t>
+          <t>36193</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8179,12 +8179,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>30,06%</t>
+          <t>31,09%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>50,68%</t>
+          <t>50,94%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8199,12 +8199,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>50655</t>
+          <t>48948</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>68895</t>
+          <t>69085</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8214,12 +8214,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>36,17%</t>
+          <t>34,95%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>49,19%</t>
+          <t>49,33%</t>
         </is>
       </c>
     </row>
@@ -8242,12 +8242,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2048</t>
+          <t>2014</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>9079</t>
+          <t>8879</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8257,12 +8257,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>13,16%</t>
+          <t>12,87%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8277,12 +8277,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>4152</t>
+          <t>4177</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>13930</t>
+          <t>14491</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8292,12 +8292,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>5,88%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>19,61%</t>
+          <t>20,4%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8312,12 +8312,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>8020</t>
+          <t>7987</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>20296</t>
+          <t>20785</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8327,12 +8327,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>14,49%</t>
+          <t>14,84%</t>
         </is>
       </c>
     </row>
@@ -8360,7 +8360,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4721</t>
+          <t>4626</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8375,7 +8375,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -8430,7 +8430,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>4703</t>
+          <t>4656</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -8445,7 +8445,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,32%</t>
         </is>
       </c>
     </row>
@@ -8473,7 +8473,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>4644</t>
+          <t>3428</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8488,7 +8488,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>6,73%</t>
+          <t>4,97%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8508,7 +8508,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>5108</t>
+          <t>5765</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -8523,7 +8523,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>7,19%</t>
+          <t>8,11%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8538,12 +8538,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>690</t>
+          <t>703</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>6202</t>
+          <t>6907</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8553,12 +8553,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,93%</t>
         </is>
       </c>
     </row>
@@ -8698,12 +8698,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>40758</t>
+          <t>41079</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>56866</t>
+          <t>57452</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8713,12 +8713,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>40,07%</t>
+          <t>40,39%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>55,91%</t>
+          <t>56,48%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8733,12 +8733,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>45163</t>
+          <t>44897</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>62514</t>
+          <t>61627</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8748,12 +8748,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>43,42%</t>
+          <t>43,17%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>60,1%</t>
+          <t>59,25%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8768,12 +8768,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>90835</t>
+          <t>91597</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>113200</t>
+          <t>114016</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8783,12 +8783,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>44,15%</t>
+          <t>44,52%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>55,02%</t>
+          <t>55,42%</t>
         </is>
       </c>
     </row>
@@ -8811,12 +8811,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>26275</t>
+          <t>25823</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>41580</t>
+          <t>40683</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8826,12 +8826,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>25,83%</t>
+          <t>25,39%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>40,88%</t>
+          <t>40,0%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8846,12 +8846,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>29339</t>
+          <t>29414</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>45949</t>
+          <t>45205</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8861,12 +8861,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>28,21%</t>
+          <t>28,28%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>44,18%</t>
+          <t>43,46%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8881,12 +8881,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>60177</t>
+          <t>59924</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>81389</t>
+          <t>81706</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8896,12 +8896,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>29,25%</t>
+          <t>29,13%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>39,56%</t>
+          <t>39,72%</t>
         </is>
       </c>
     </row>
@@ -8924,12 +8924,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>11749</t>
+          <t>11917</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>23215</t>
+          <t>23317</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8939,12 +8939,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>11,55%</t>
+          <t>11,72%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>22,82%</t>
+          <t>22,92%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8959,12 +8959,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>6288</t>
+          <t>6077</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>16475</t>
+          <t>16793</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8974,12 +8974,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>5,84%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>15,84%</t>
+          <t>16,15%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8994,12 +8994,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>19998</t>
+          <t>20041</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>35159</t>
+          <t>35895</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9009,12 +9009,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>9,72%</t>
+          <t>9,74%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>17,09%</t>
+          <t>17,45%</t>
         </is>
       </c>
     </row>
@@ -9042,7 +9042,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3689</t>
+          <t>4263</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9057,7 +9057,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9077,7 +9077,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>4497</t>
+          <t>4633</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9092,7 +9092,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9107,12 +9107,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>615</t>
+          <t>648</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>6586</t>
+          <t>6833</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9122,12 +9122,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,32%</t>
         </is>
       </c>
     </row>
@@ -9150,62 +9150,62 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
+          <t>556</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>4846</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>1,78%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>0,55%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>4,76%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>1405</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>4305</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>1,78%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>4800</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>1,35%</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>4,23%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>1405</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>4338</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>1,35%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1198</t>
+          <t>1303</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>7292</t>
+          <t>7867</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9235,12 +9235,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,82%</t>
         </is>
       </c>
     </row>
@@ -9380,12 +9380,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>32432</t>
+          <t>32198</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>44792</t>
+          <t>45935</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -9395,12 +9395,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>47,23%</t>
+          <t>46,89%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>65,23%</t>
+          <t>66,9%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9415,12 +9415,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>30663</t>
+          <t>30701</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>45286</t>
+          <t>45100</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9430,12 +9430,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>41,09%</t>
+          <t>41,14%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>60,69%</t>
+          <t>60,44%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9450,12 +9450,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>67158</t>
+          <t>66399</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>86233</t>
+          <t>86103</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9465,12 +9465,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>46,87%</t>
+          <t>46,34%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>60,18%</t>
+          <t>60,09%</t>
         </is>
       </c>
     </row>
@@ -9498,7 +9498,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>30430</t>
+          <t>30556</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9513,7 +9513,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>44,32%</t>
+          <t>44,5%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9528,12 +9528,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>16954</t>
+          <t>17207</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>30832</t>
+          <t>30291</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9543,12 +9543,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>22,72%</t>
+          <t>23,06%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>41,32%</t>
+          <t>40,59%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9563,12 +9563,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>37842</t>
+          <t>38045</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>56173</t>
+          <t>56696</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9578,12 +9578,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>26,41%</t>
+          <t>26,55%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>39,2%</t>
+          <t>39,57%</t>
         </is>
       </c>
     </row>
@@ -9606,12 +9606,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1559</t>
+          <t>1605</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>8705</t>
+          <t>8958</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9621,12 +9621,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>12,68%</t>
+          <t>13,05%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9641,12 +9641,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>5827</t>
+          <t>5929</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>16097</t>
+          <t>15615</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9656,12 +9656,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>7,81%</t>
+          <t>7,95%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>21,57%</t>
+          <t>20,93%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9676,12 +9676,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>8728</t>
+          <t>9472</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>21204</t>
+          <t>22084</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9691,12 +9691,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>6,61%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>14,8%</t>
+          <t>15,41%</t>
         </is>
       </c>
     </row>
@@ -9724,7 +9724,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5276</t>
+          <t>5050</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9739,7 +9739,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>7,68%</t>
+          <t>7,36%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9759,7 +9759,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>3804</t>
+          <t>3806</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9789,12 +9789,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>662</t>
+          <t>658</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>6975</t>
+          <t>6147</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9809,7 +9809,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>4,29%</t>
         </is>
       </c>
     </row>
@@ -9867,12 +9867,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>694</t>
+          <t>693</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>7450</t>
+          <t>6523</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9887,7 +9887,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>9,98%</t>
+          <t>8,74%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9902,12 +9902,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>691</t>
+          <t>693</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>6591</t>
+          <t>6983</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9922,7 +9922,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,87%</t>
         </is>
       </c>
     </row>
@@ -10062,12 +10062,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>45826</t>
+          <t>45129</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>63951</t>
+          <t>63470</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10077,12 +10077,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>44,11%</t>
+          <t>43,44%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>61,56%</t>
+          <t>61,1%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10097,12 +10097,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>29720</t>
+          <t>30553</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>47059</t>
+          <t>46437</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10112,12 +10112,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>30,29%</t>
+          <t>31,14%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>47,97%</t>
+          <t>47,34%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10132,12 +10132,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>80617</t>
+          <t>81231</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>105161</t>
+          <t>107148</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10147,12 +10147,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>39,91%</t>
+          <t>40,22%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>52,06%</t>
+          <t>53,05%</t>
         </is>
       </c>
     </row>
@@ -10175,12 +10175,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>33270</t>
+          <t>33387</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>50141</t>
+          <t>51528</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10190,12 +10190,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>32,03%</t>
+          <t>32,14%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>48,27%</t>
+          <t>49,6%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10210,12 +10210,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>35421</t>
+          <t>35033</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>51711</t>
+          <t>51426</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10225,12 +10225,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>36,11%</t>
+          <t>35,71%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>52,71%</t>
+          <t>52,42%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10245,12 +10245,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>73176</t>
+          <t>71942</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>97142</t>
+          <t>97357</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10260,12 +10260,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>36,23%</t>
+          <t>35,62%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>48,09%</t>
+          <t>48,2%</t>
         </is>
       </c>
     </row>
@@ -10288,47 +10288,47 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>832</t>
+          <t>1485</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
+          <t>8410</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>3,69%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>1,43%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>8,1%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>13186</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
           <t>8149</t>
         </is>
       </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>3,69%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>0,8%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>7,84%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>13186</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>8247</t>
-        </is>
-      </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>20189</t>
+          <t>19380</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10338,12 +10338,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>8,41%</t>
+          <t>8,31%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>20,58%</t>
+          <t>19,76%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -10358,12 +10358,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>11317</t>
+          <t>11380</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>24789</t>
+          <t>24459</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -10373,12 +10373,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>12,27%</t>
+          <t>12,11%</t>
         </is>
       </c>
     </row>
@@ -10401,12 +10401,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>831</t>
+          <t>983</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>7793</t>
+          <t>7978</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>7,68%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -10436,12 +10436,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1423</t>
+          <t>1394</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>8120</t>
+          <t>7906</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -10451,12 +10451,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>8,28%</t>
+          <t>8,06%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10471,12 +10471,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>3303</t>
+          <t>3528</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>11932</t>
+          <t>12582</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -10486,12 +10486,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>6,23%</t>
         </is>
       </c>
     </row>
@@ -10744,12 +10744,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>159248</t>
+          <t>158796</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>190111</t>
+          <t>189840</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10759,12 +10759,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>46,39%</t>
+          <t>46,26%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>55,38%</t>
+          <t>55,3%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10779,12 +10779,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>146334</t>
+          <t>146506</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>177312</t>
+          <t>178418</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10794,12 +10794,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>42,08%</t>
+          <t>42,13%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>50,98%</t>
+          <t>51,3%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10814,12 +10814,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>314395</t>
+          <t>316591</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>361213</t>
+          <t>359336</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10829,12 +10829,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>45,5%</t>
+          <t>45,81%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>52,27%</t>
+          <t>52,0%</t>
         </is>
       </c>
     </row>
@@ -10857,12 +10857,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>114366</t>
+          <t>114357</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>144579</t>
+          <t>143664</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10872,12 +10872,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>33,32%</t>
+          <t>33,31%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>42,12%</t>
+          <t>41,85%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10892,12 +10892,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>117848</t>
+          <t>118900</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>148280</t>
+          <t>147762</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10907,12 +10907,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>33,89%</t>
+          <t>34,19%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>42,64%</t>
+          <t>42,49%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10927,12 +10927,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>241557</t>
+          <t>239399</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>283297</t>
+          <t>280912</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10942,12 +10942,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>34,96%</t>
+          <t>34,64%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>41,0%</t>
+          <t>40,65%</t>
         </is>
       </c>
     </row>
@@ -10970,12 +10970,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>22038</t>
+          <t>22442</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>39044</t>
+          <t>40111</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10985,12 +10985,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>6,54%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>11,37%</t>
+          <t>11,69%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -11005,12 +11005,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>32590</t>
+          <t>32658</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>53024</t>
+          <t>53498</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -11020,12 +11020,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>9,37%</t>
+          <t>9,39%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>15,25%</t>
+          <t>15,38%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -11040,12 +11040,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>58115</t>
+          <t>59180</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>85592</t>
+          <t>85692</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -11055,12 +11055,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>8,41%</t>
+          <t>8,56%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>12,39%</t>
+          <t>12,4%</t>
         </is>
       </c>
     </row>
@@ -11083,12 +11083,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>3986</t>
+          <t>3869</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>13228</t>
+          <t>12803</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -11098,12 +11098,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -11118,12 +11118,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>2934</t>
+          <t>2826</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>11120</t>
+          <t>10911</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -11133,12 +11133,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -11153,12 +11153,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>8243</t>
+          <t>8376</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>21159</t>
+          <t>20074</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -11168,12 +11168,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>2,9%</t>
         </is>
       </c>
     </row>
@@ -11196,12 +11196,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>626</t>
+          <t>628</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>6551</t>
+          <t>6605</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -11216,7 +11216,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -11231,12 +11231,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>2183</t>
+          <t>2204</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>10609</t>
+          <t>10086</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -11251,7 +11251,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -11266,12 +11266,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>4273</t>
+          <t>4052</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>13835</t>
+          <t>13740</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -11281,12 +11281,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,99%</t>
         </is>
       </c>
     </row>
